--- a/backend/uploads/qa_generated/RGP-Test_case_242a9d10.xlsx
+++ b/backend/uploads/qa_generated/RGP-Test_case_242a9d10.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +34,25 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Browallia New"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Browallia New"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Browallia New"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -54,8 +71,20 @@
         <bgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CDEEFF"/>
+        <bgColor rgb="00CDEEFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -77,11 +106,149 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+    </border>
+    <border/>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0C4DE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0C4DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0C4DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0C4DE"/>
+      </bottom>
+    </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -99,6 +266,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,410 +715,323 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SPECTRA QA PLATFORM - RGP-Test case (Test Case)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="7" t="n"/>
+      <c r="G1" s="7" t="n"/>
+      <c r="H1" s="7" t="n"/>
+      <c r="I1" s="7" t="n"/>
+      <c r="J1" s="7" t="n"/>
+      <c r="K1" s="7" t="n"/>
+      <c r="L1" s="7" t="n"/>
+      <c r="M1" s="7" t="n"/>
+      <c r="N1" s="7" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="n"/>
+      <c r="K2" s="7" t="n"/>
+      <c r="L2" s="7" t="n"/>
+      <c r="M2" s="7" t="n"/>
+      <c r="N2" s="7" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="n"/>
+      <c r="L3" s="7" t="n"/>
+      <c r="M3" s="7" t="n"/>
+      <c r="N3" s="7" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="7" t="n"/>
+      <c r="L4" s="7" t="n"/>
+      <c r="M4" s="7" t="n"/>
+      <c r="N4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>TIFFA-RGP (69A)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="D6" s="38" t="inlineStr">
+        <is>
+          <t>FoodSmile</t>
+        </is>
+      </c>
+      <c r="E6" s="38" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>Create Date :</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="38" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n"/>
-    </row>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Module / Function:</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Restricted Goods Permit (LPI), Declaration, User Profile</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Test Engine:</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Spectra AI (Gemini 3.1 Pro)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="2" t="inlineStr">
+      <c r="J6" s="38" t="n"/>
+      <c r="K6" s="38" t="n"/>
+      <c r="L6" s="38" t="n"/>
+      <c r="M6" s="38" t="n"/>
+      <c r="N6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="17" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Project ID:</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Start Test Date :</t>
+        </is>
+      </c>
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="38" t="inlineStr">
+        <is>
+          <t>Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="J8" s="38" t="n"/>
+      <c r="K8" s="38" t="n"/>
+      <c r="L8" s="38" t="n"/>
+      <c r="M8" s="38" t="n"/>
+      <c r="N8" s="17" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TC_RGP_001</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="16" t="n"/>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="16" t="n"/>
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="16" t="n"/>
+      <c r="N9" s="17" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TC_RGP_002</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Tester Name :</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Status :</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Baseline Specification</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Test ID</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Test Objective</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Test Description / Procedure</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Req No.</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Updated By</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>TC_RGP_001</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Verify that a user can successfully create an LPI by linking an existing Invoice.</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>1. Log in to the system.
-2. Navigate to the Permit menu.
-3. Click 'Create LPI'.
-4. Select an existing Invoice from the list.
-5. Fill in the required permit details.
-6. Click 'Save'.</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Username: user@tiffa.com
-Password: password123
-Invoice No: INV-2025-001</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>The system successfully creates the LPI, links it to INV-2025-001, and displays the status as 'Draft'.</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>REQ-001</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>TC_RGP_002</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Verify that the system prevents LPI creation if no Invoice is linked.</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>1. Log in to the system.
-2. Navigate to the Permit menu.
-3. Click 'Create LPI'.
-4. Do not select or create any Invoice.
-5. Attempt to fill in permit details and click 'Save'.</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="38" t="inlineStr">
         <is>
           <t>Username: user@tiffa.com
 Password: password123</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>The system disables the 'Save' button or displays an error message 'Please select or create an Invoice before creating an LPI.'</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>REQ-001</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+      <c r="E10" s="38" t="n"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Finish Test Date :</t>
+        </is>
+      </c>
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="38" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="J10" s="38" t="n"/>
+      <c r="K10" s="38" t="n"/>
+      <c r="L10" s="38" t="n"/>
+      <c r="M10" s="38" t="n"/>
+      <c r="N10" s="17" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_003</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Verify that the system correctly identifies restricted goods based on the 8-digit HS Code.</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>1. Navigate to the Invoice creation/edit page.
-2. Add a product line item.
-3. Enter an 8-digit HS Code known to require a permit (e.g., FDA controlled).
-4. Save the line item.</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>HS Code: 39191010 (FDA controlled)</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>The system flags the product, displays an alert icon indicating a permit is required, and identifies the relevant department (e.g., FDA/อย.).</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>REQ-002</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="16" t="n"/>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="16" t="n"/>
+      <c r="N11" s="17" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_004</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Verify that the system blocks customs declaration submission if all required permits are not in 'Accept' status.</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>1. Navigate to the Import Declaration menu.
-2. Select a declaration containing restricted goods that require multiple permits.
-3. Ensure at least one permit is still in 'Draft' or 'Sent' status (not 'Accept').
-4. Click 'Submit Declaration'.</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Project Release / Version :</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="inlineStr">
         <is>
           <t>Declaration No: DRAFT-DEC-001
 Permit 1 Status: Accept
 Permit 2 Status: Draft</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>The system blocks the submission and displays an error message 'Cannot submit declaration. All required permits must be approved first.'</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>REQ-003</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+      <c r="E12" s="38" t="n"/>
+      <c r="F12" s="38" t="n"/>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module / Function: </t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="38" t="inlineStr">
+        <is>
+          <t>Test Cases</t>
+        </is>
+      </c>
+      <c r="J12" s="38" t="n"/>
+      <c r="K12" s="38" t="n"/>
+      <c r="L12" s="38" t="n"/>
+      <c r="M12" s="38" t="n"/>
+      <c r="N12" s="17" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_005</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Verify dynamic show/hide of mandatory fields based on the selected government department.</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>1. Navigate to the Permit creation page.
-2. Select 'FDA (อย.)' as the target department.
-3. Observe the displayed fields.
-4. Change the target department to 'Rubber Authority'.
-5. Observe the displayed fields.</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Department 1: FDA (อย.)
-Department 2: Rubber Authority</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>The form dynamically updates to show only the mandatory fields required by the selected department, hiding irrelevant fields.</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>REQ-004</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+      <c r="B13" s="40" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="26" t="n"/>
+      <c r="F13" s="26" t="n"/>
+      <c r="G13" s="26" t="n"/>
+      <c r="H13" s="26" t="n"/>
+      <c r="I13" s="26" t="n"/>
+      <c r="J13" s="26" t="n"/>
+      <c r="K13" s="26" t="n"/>
+      <c r="L13" s="26" t="n"/>
+      <c r="M13" s="26" t="n"/>
+      <c r="N13" s="27" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_006</t>
@@ -917,57 +1081,34 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_007</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Verify the system enforces the One Invoice = One Permit (LPI) rule.</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>1. Navigate to the Permit menu.
-2. Click 'Create LPI'.
-3. Select an Invoice that is already linked to an existing active LPI.
-4. Attempt to save.</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Invoice No: INV-2025-002 (Already linked to LPI-2025-001)</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>The system prevents the selection of the invoice or displays an error 'This invoice is already linked to another permit. One Invoice = One Permit rule applies.'</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>REQ-006</t>
-        </is>
-      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUNCTIONAL REQUIREMENTS (Requirements No.) :</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="32" t="n"/>
+      <c r="H15" s="33" t="n"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>AI Agent</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="12" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_008</t>
@@ -1017,68 +1158,90 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_009</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Verify the system rejects Reference Customs Declaration Numbers for permit creation.</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>1. Navigate to the Permit menu.
-2. Choose to create a permit from a customs declaration.
-3. Enter a finalized Reference Customs Declaration Number.
-4. Proceed with creation.</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Reference Declaration No: REF-2025-8877</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>The system rejects the number and displays an error 'Permits must be created using a Draft declaration number, not a Reference number.'</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>REQ-001</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>Test Case Objective</t>
+        </is>
+      </c>
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>Test Step</t>
+        </is>
+      </c>
+      <c r="E17" s="34" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>Test Type</t>
+        </is>
+      </c>
+      <c r="G17" s="34" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="H17" s="34" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I17" s="34" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J17" s="34" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+      <c r="K17" s="34" t="inlineStr">
+        <is>
+          <t>Automate</t>
+        </is>
+      </c>
+      <c r="L17" s="34" t="inlineStr">
+        <is>
+          <t>Req No.</t>
+        </is>
+      </c>
+      <c r="M17" s="34" t="inlineStr">
+        <is>
+          <t>Platforms</t>
+        </is>
+      </c>
+      <c r="N17" s="34" t="inlineStr">
+        <is>
+          <t>Updated By</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="180" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_010</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>Verify that an Attorney can switch company contexts and data is filtered accordingly.</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>1. Log in as an Attorney affiliated with Company A and Company B.
 2. Select Company A context.
@@ -1087,51 +1250,69 @@
 5. Verify available invoices/data.</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>Attorney User: attorney@tiffa.com
 Company A: Siam Trading
 Company B: Thai Export</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>The system successfully switches context without session loss, and strictly filters invoices and data to match the currently selected company.</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="F18" s="35" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="G18" s="36" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="H18" s="36" t="inlineStr"/>
+      <c r="I18" s="35" t="inlineStr"/>
+      <c r="J18" s="36" t="inlineStr">
         <is>
           <t>REQ-007</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
+      <c r="K18" s="35" t="inlineStr">
+        <is>
+          <t>AI AGENT</t>
+        </is>
+      </c>
+      <c r="L18" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M18" s="35" t="inlineStr">
+        <is>
+          <t>Web Application</t>
+        </is>
+      </c>
+      <c r="N18" s="35" t="inlineStr">
+        <is>
+          <t>Username: user@tiffa.com
+Password: password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="180" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_011</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>Verify that users can split invoice lines for the same product and lot number.</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>1. Open an Invoice.
 2. Add a product line item with a specific Lot Number and Quantity.
@@ -1139,7 +1320,7 @@
 4. Save the invoice.</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>Product: PRD-001
 Lot No: LOT-A1
@@ -1147,44 +1328,62 @@
 Line 2 Qty: 50</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>The system allows multiple line items for the exact same product and lot number without throwing a duplicate error.</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="F19" s="35" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="G19" s="36" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="H19" s="36" t="inlineStr"/>
+      <c r="I19" s="35" t="inlineStr"/>
+      <c r="J19" s="36" t="inlineStr">
         <is>
           <t>REQ-002</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+      <c r="K19" s="35" t="inlineStr">
+        <is>
+          <t>AI AGENT</t>
+        </is>
+      </c>
+      <c r="L19" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M19" s="35" t="inlineStr">
+        <is>
+          <t>Web Application</t>
+        </is>
+      </c>
+      <c r="N19" s="35" t="inlineStr">
+        <is>
+          <t>Username: user@tiffa.com
+Password: password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="180" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_012</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Verify Attorney ID configuration behavior for internal vs external processing.</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>1. Open a Permit request.
 2. Select 'Internal Processing' (Self-process).
@@ -1194,99 +1393,135 @@
 6. Select an Attorney from the dropdown/CIS list.</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>Internal User: admin@company.com
 External Attorney: attorney@agency.com</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>For internal, Attorney ID is hidden/optional. For external, the field is not a free-text box and correctly fetches data from Local Customer/CIS records.</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="G20" s="36" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="H20" s="36" t="inlineStr"/>
+      <c r="I20" s="35" t="inlineStr"/>
+      <c r="J20" s="36" t="inlineStr">
         <is>
           <t>REQ-003</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+      <c r="K20" s="35" t="inlineStr">
+        <is>
+          <t>AI AGENT</t>
+        </is>
+      </c>
+      <c r="L20" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M20" s="35" t="inlineStr">
+        <is>
+          <t>Web Application</t>
+        </is>
+      </c>
+      <c r="N20" s="35" t="inlineStr">
+        <is>
+          <t>Username: user@tiffa.com
+Password: password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="133" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_013</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Verify visibility of Dynamic Master License Types.</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
         <is>
           <t>1. Navigate to the Permit request form.
 2. Click on the 'License Type' dropdown.
 3. Verify the available options.</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="36" t="inlineStr">
         <is>
           <t>Expected visible types: 0, 1, 2</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="36" t="inlineStr">
         <is>
           <t>Only License Types 0, 1, and 2 are visible by default. Types 3-7 are hidden.</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="G21" s="36" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="H21" s="36" t="inlineStr"/>
+      <c r="I21" s="35" t="inlineStr"/>
+      <c r="J21" s="36" t="inlineStr">
         <is>
           <t>REQ-005</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
+      <c r="K21" s="35" t="inlineStr">
+        <is>
+          <t>AI AGENT</t>
+        </is>
+      </c>
+      <c r="L21" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M21" s="35" t="inlineStr">
+        <is>
+          <t>Web Application</t>
+        </is>
+      </c>
+      <c r="N21" s="35" t="inlineStr">
+        <is>
+          <t>Username: user@tiffa.com
+Password: password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="180" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_014</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>Verify Product Origin auto-population from Product Master File.</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="36" t="inlineStr">
         <is>
           <t>1. Open a Permit request form.
 2. Select a product that has an Origin defined in the Master File.
@@ -1295,149 +1530,203 @@
 5. Observe the 'Origin' field.</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="36" t="inlineStr">
         <is>
           <t>Product w/ Origin: PRD-TH (Origin: TH)
 Product w/o Origin: PRD-NULL</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t>For PRD-TH, the Origin field auto-fills with 'TH'. For PRD-NULL, the field remains blank and is editable by the user.</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="G22" s="36" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="H22" s="36" t="inlineStr"/>
+      <c r="I22" s="35" t="inlineStr"/>
+      <c r="J22" s="36" t="inlineStr">
         <is>
           <t>REQ-008</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+      <c r="K22" s="35" t="inlineStr">
+        <is>
+          <t>AI AGENT</t>
+        </is>
+      </c>
+      <c r="L22" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M22" s="35" t="inlineStr">
+        <is>
+          <t>Web Application</t>
+        </is>
+      </c>
+      <c r="N22" s="35" t="inlineStr">
+        <is>
+          <t>Username: user@tiffa.com
+Password: password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="171" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_015</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Verify Permit Re-request logic for modified products.</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="36" t="inlineStr">
         <is>
           <t>1. Select an existing product for import that already has a valid permit.
 2. Check the flag indicating a change in packaging/formula.
 3. Attempt to proceed with the import.</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="36" t="inlineStr">
         <is>
           <t>Product: PRD-001
 Change Flag: True (Packaging changed)</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="36" t="inlineStr">
         <is>
           <t>The system prompts the user that a completely new permit request is required due to the modifications.</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="G23" s="36" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="H23" s="36" t="inlineStr"/>
+      <c r="I23" s="35" t="inlineStr"/>
+      <c r="J23" s="36" t="inlineStr">
         <is>
           <t>REQ-009</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
+      <c r="K23" s="35" t="inlineStr">
+        <is>
+          <t>AI AGENT</t>
+        </is>
+      </c>
+      <c r="L23" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M23" s="35" t="inlineStr">
+        <is>
+          <t>Web Application</t>
+        </is>
+      </c>
+      <c r="N23" s="35" t="inlineStr">
+        <is>
+          <t>Username: user@tiffa.com
+Password: password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="152" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_016</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Verify Permit Dashboard display and sorting rules.</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>1. Navigate to the Permit Dashboard.
 2. Observe the sorting order of the displayed permits.
 3. Look for permits with 'Completed' or 'Finished' status.</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>Permits with statuses: Draft, Sent, Error, Completed</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr">
         <is>
           <t>The latest updated records appear at the top. Permits with 'Completed' status are hidden from the main dashboard view.</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="F24" s="35" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="G24" s="36" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="H24" s="36" t="inlineStr"/>
+      <c r="I24" s="35" t="inlineStr"/>
+      <c r="J24" s="36" t="inlineStr">
         <is>
           <t>REQ-010</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
+      <c r="K24" s="35" t="inlineStr">
+        <is>
+          <t>AI AGENT</t>
+        </is>
+      </c>
+      <c r="L24" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M24" s="35" t="inlineStr">
+        <is>
+          <t>Web Application</t>
+        </is>
+      </c>
+      <c r="N24" s="35" t="inlineStr">
+        <is>
+          <t>Username: user@tiffa.com
+Password: password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="180" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_017</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Verify successful Permit Cancellation for an 'Accepted' permit.</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>1. Open a Permit with 'Accepted' status (and no declaration sent).
 2. Click 'Cancel'.
@@ -1445,100 +1734,136 @@
 4. Submit the cancellation.</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="36" t="inlineStr">
         <is>
           <t>Permit Status: Accepted
 Reason: Reason 3 (Data Error)</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="36" t="inlineStr">
         <is>
           <t>The system accepts the cancellation, updates the status to 'Canceled', and logs the user and reason in the database.</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="F25" s="35" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="G25" s="36" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="H25" s="36" t="inlineStr"/>
+      <c r="I25" s="35" t="inlineStr"/>
+      <c r="J25" s="36" t="inlineStr">
         <is>
           <t>REQ-011</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+      <c r="K25" s="35" t="inlineStr">
+        <is>
+          <t>AI AGENT</t>
+        </is>
+      </c>
+      <c r="L25" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" s="35" t="inlineStr">
+        <is>
+          <t>Web Application</t>
+        </is>
+      </c>
+      <c r="N25" s="35" t="inlineStr">
+        <is>
+          <t>Username: user@tiffa.com
+Password: password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="133" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_018</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>Verify Permit Cancellation is blocked if the customs declaration is already sent.</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
         <is>
           <t>1. Open a Permit with 'Accepted' status.
 2. Ensure the linked customs declaration has been sent/processed.
 3. Click 'Cancel'.</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="36" t="inlineStr">
         <is>
           <t>Permit Status: Accepted
 Linked Declaration Status: Sent</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="36" t="inlineStr">
         <is>
           <t>The system blocks the cancellation and displays an alert 'Cannot cancel permit. Customs declaration has already been sent. Please cancel the declaration first.'</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="F26" s="35" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="G26" s="36" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="H26" s="36" t="inlineStr"/>
+      <c r="I26" s="35" t="inlineStr"/>
+      <c r="J26" s="36" t="inlineStr">
         <is>
           <t>REQ-011</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+      <c r="K26" s="35" t="inlineStr">
+        <is>
+          <t>AI AGENT</t>
+        </is>
+      </c>
+      <c r="L26" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" s="35" t="inlineStr">
+        <is>
+          <t>Web Application</t>
+        </is>
+      </c>
+      <c r="N26" s="35" t="inlineStr">
+        <is>
+          <t>Username: user@tiffa.com
+Password: password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="180" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_019</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>Verify Special Case Permit Handling bypasses reason requirement and doesn't update Master.</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>1. Initiate a 'Special Case' permit request for an HS Code that normally doesn't require one.
 2. Leave the 'Reason for Request' blank.
@@ -1546,99 +1871,135 @@
 4. Check the Product Master File for that HS Code.</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="36" t="inlineStr">
         <is>
           <t>HS Code: 99999999 (Not restricted)</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="36" t="inlineStr">
         <is>
           <t>The system processes the permit without validation errors for the missing reason. The Product Master File remains unchanged (HS Code is not marked as restricted).</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="F27" s="35" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="G27" s="36" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="H27" s="36" t="inlineStr"/>
+      <c r="I27" s="35" t="inlineStr"/>
+      <c r="J27" s="36" t="inlineStr">
         <is>
           <t>REQ-013</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
+      <c r="K27" s="35" t="inlineStr">
+        <is>
+          <t>AI AGENT</t>
+        </is>
+      </c>
+      <c r="L27" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M27" s="35" t="inlineStr">
+        <is>
+          <t>Web Application</t>
+        </is>
+      </c>
+      <c r="N27" s="35" t="inlineStr">
+        <is>
+          <t>Username: user@tiffa.com
+Password: password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="152" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_020</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>Verify that processed LPIs are locked and read-only.</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
         <is>
           <t>1. Navigate to an LPI that is linked to a processed/completed customs declaration.
 2. Open the LPI details.
 3. Attempt to edit or cancel the LPI.</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="36" t="inlineStr">
         <is>
           <t>LPI Status: Completed
 Linked Declaration Status: Completed</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="36" t="inlineStr">
         <is>
           <t>The system hides or disables the Edit and Cancel buttons. The LPI data is strictly read-only.</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="F28" s="35" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="G28" s="36" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="H28" s="36" t="inlineStr"/>
+      <c r="I28" s="35" t="inlineStr"/>
+      <c r="J28" s="36" t="inlineStr">
         <is>
           <t>REQ-005</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+      <c r="K28" s="35" t="inlineStr">
+        <is>
+          <t>AI AGENT</t>
+        </is>
+      </c>
+      <c r="L28" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M28" s="35" t="inlineStr">
+        <is>
+          <t>Web Application</t>
+        </is>
+      </c>
+      <c r="N28" s="35" t="inlineStr">
+        <is>
+          <t>Username: user@tiffa.com
+Password: password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="180" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_021</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>Verify module access sequencing (LPI requires Invoice module).</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
         <is>
           <t>1. Log in as an Admin.
 2. Navigate to Client Module Subscriptions.
@@ -1646,50 +2007,68 @@
 4. Attempt to activate the 'LPI' module for that client.</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="36" t="inlineStr">
         <is>
           <t>Client: Test Company
 Invoice Module: Inactive</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="36" t="inlineStr">
         <is>
           <t>The system prevents the activation of the LPI module and displays a warning 'Prerequisite Invoice module must be active.'</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="F29" s="35" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="G29" s="36" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="H29" s="36" t="inlineStr"/>
+      <c r="I29" s="35" t="inlineStr"/>
+      <c r="J29" s="36" t="inlineStr">
         <is>
           <t>REQ-012</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
+      <c r="K29" s="35" t="inlineStr">
+        <is>
+          <t>AI AGENT</t>
+        </is>
+      </c>
+      <c r="L29" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" s="35" t="inlineStr">
+        <is>
+          <t>Web Application</t>
+        </is>
+      </c>
+      <c r="N29" s="35" t="inlineStr">
+        <is>
+          <t>Username: user@tiffa.com
+Password: password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="180" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_022</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>Verify Employee Resignation and Data Replacement function.</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>1. Log in as Company Admin.
 2. Navigate to User Management.
@@ -1698,97 +2077,146 @@
 5. Verify the reassignment of tasks/data.</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="36" t="inlineStr">
         <is>
           <t>Resigned User: old_emp@company.com
 Replacement User: new_emp@company.com</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="36" t="inlineStr">
         <is>
           <t>The resigned user's access is revoked. All active LPIs, tasks, and relevant data are successfully transferred to the replacement user.</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="G30" s="36" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="H30" s="36" t="inlineStr"/>
+      <c r="I30" s="35" t="inlineStr"/>
+      <c r="J30" s="36" t="inlineStr">
         <is>
           <t>REQ-008</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
+      <c r="K30" s="35" t="inlineStr">
+        <is>
+          <t>AI AGENT</t>
+        </is>
+      </c>
+      <c r="L30" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" s="35" t="inlineStr">
+        <is>
+          <t>Web Application</t>
+        </is>
+      </c>
+      <c r="N30" s="35" t="inlineStr">
+        <is>
+          <t>Username: user@tiffa.com
+Password: password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="152" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>TC_RGP_023</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Verify FDA (อย.) System Integration Testing Scenario.</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>1. Create a complete and valid Restricted Goods Permit request for the FDA.
 2. Click 'Submit to NSW'.
 3. Monitor the EzyBUS exchange logs and the Permit status.</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="36" t="inlineStr">
         <is>
           <t>Target Agency: FDA (อย.)
 Valid XML Payload</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="36" t="inlineStr">
         <is>
           <t>The system successfully generates FDA-compliant XML, transmits it to the FDA test environment via EzyBUS/NSP, and receives an acknowledgment/response, updating the status accordingly.</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>[-]</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="F31" s="35" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="G31" s="36" t="inlineStr">
+        <is>
+          <t>[-]</t>
+        </is>
+      </c>
+      <c r="H31" s="36" t="inlineStr"/>
+      <c r="I31" s="35" t="inlineStr"/>
+      <c r="J31" s="36" t="inlineStr">
         <is>
           <t>REQ-010</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
+      <c r="K31" s="35" t="inlineStr">
+        <is>
+          <t>AI AGENT</t>
+        </is>
+      </c>
+      <c r="L31" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" s="35" t="inlineStr">
+        <is>
+          <t>Web Application</t>
+        </is>
+      </c>
+      <c r="N31" s="35" t="inlineStr">
+        <is>
+          <t>Username: user@tiffa.com
+Password: password123</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="20">
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I12:M12"/>
+    <mergeCell ref="B1:N4"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="D10:F10"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="I10:M10"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
